--- a/data/CReDEs/v4/dg_ryjl.xlsx
+++ b/data/CReDEs/v4/dg_ryjl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B11F65F-E851-4FDA-BBFD-1C45BCBC0CF3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A931F-2260-47AB-9539-038117A31752}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{90C59CE8-86F0-4EB7-BEF2-A51889E772A3}"/>
   </bookViews>
@@ -471,10 +471,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写符合描述的内容，单位为“个”，若没有描述则填写"未描述"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>请填写符合描述的内容，单位为“cm”，若没有描述则填写"未描述",请填写符合描述的内容，单位为“cm”，若没有描述则填写"未描述"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -512,6 +508,10 @@
   </si>
   <si>
     <t>请填写以下选项：是，否，未描述,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1542,7 +1542,7 @@
         <v>29</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1563,7 +1563,7 @@
         <v>71</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1599,13 +1599,13 @@
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -1641,13 +1641,13 @@
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="G34" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>43</v>
@@ -1689,7 +1689,7 @@
         <v>29</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -1704,13 +1704,13 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/data/CReDEs/v4/dg_ryjl.xlsx
+++ b/data/CReDEs/v4/dg_ryjl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A931F-2260-47AB-9539-038117A31752}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D9AA63-318E-4934-8835-33AD857886A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{90C59CE8-86F0-4EB7-BEF2-A51889E772A3}"/>
   </bookViews>
@@ -495,10 +495,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写以下选项：是，否，未描述,请填写以下选项：是，否，未描述,请填写以下选项：无，左支，右支，主干，未描述,请填写以下选项：无，左支，右支，主干,未描述,请填写以下选项：无，有，未描述,</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CT检查结果：平扫期是否增强,CT检查结果：延迟期是否增强,CT检查结果：静脉期是否增强,CT检查结果：动脉期是否增强</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -512,6 +508,10 @@
   </si>
   <si>
     <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，轻，中，重，未查，未描述,请填写以下选项：是，否，未描述,请填写以下选项：无，左支，右支，主干，未描述,请填写以下选项：无，左支，右支，主干,未描述,请填写以下选项：无，有，未描述,</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1542,7 +1542,7 @@
         <v>29</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1647,7 +1647,7 @@
         <v>134</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>43</v>
@@ -1704,13 +1704,13 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
